--- a/Eggy Cup 87-93.xlsx
+++ b/Eggy Cup 87-93.xlsx
@@ -745,10 +745,8 @@
           <t>justMaki</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>25347</v>
       </c>
     </row>
     <row r="7">
